--- a/data/ordbok_konfidensialitet.xlsx
+++ b/data/ordbok_konfidensialitet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ssbno-my.sharepoint.com/personal/ibi_ssb_no/Documents/Skrivebord/Ordbok Ingrid/Utkast ordbok/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51D75198-4989-451C-92A0-C525E0952263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="245" documentId="8_{19116777-D8DD-4556-9A16-9CDC6F0D346F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EF8CADD-821F-4779-B0C7-28DB987C048F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="91">
   <si>
     <t>Ordbok for konfidensialitetsbegreper</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Emnelapp</t>
   </si>
   <si>
-    <t>Kilde</t>
-  </si>
-  <si>
     <t>Merknad</t>
   </si>
   <si>
@@ -74,9 +71,6 @@
     <t>Attribution</t>
   </si>
   <si>
-    <t>Avidentifisert datasett</t>
-  </si>
-  <si>
     <t>Avsløring</t>
   </si>
   <si>
@@ -182,12 +176,6 @@
     <t>Anonymiserte opplysninger er ikke personopplysninger og reguleres ikke av personvernlovgivningen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Situasjon som oppstår dersom en person eller organisasjon ved hjelp av data oppdager eller lærer noe den ikke visste fra før om en statistisk enhet. </t>
-  </si>
-  <si>
-    <t>Angriper</t>
-  </si>
-  <si>
     <t>Hundepool et al, s. 212</t>
   </si>
   <si>
@@ -212,9 +200,6 @@
     <t>Person eller organisasjon som forsøker å avsløre informasjon om en statistisk enhet.</t>
   </si>
   <si>
-    <t>Hundepool et al, s. 213, Heldal (Ordliste)</t>
-  </si>
-  <si>
     <t xml:space="preserve">En metode der ulike tabeller som har felles variabler sammenlignes eller kombineres for å utlede informasjon om en statistisk enhet. </t>
   </si>
   <si>
@@ -224,6 +209,9 @@
     <t>Hundepool et al, s. 215; Heldal (Ordliste)</t>
   </si>
   <si>
+    <t>Variabel som alene eller i kombinasjon er strukturelt unik(e) og dermed kan brukes til å identifisere statistiske enheter i et datasett.</t>
+  </si>
+  <si>
     <t>Regel som sier at en celle må undertrykkes dersom de n største enhetene bidrar med mer enn k% av celletotalen. Verdiene for n og k fastsettes av statistikkmyndigheten.</t>
   </si>
   <si>
@@ -248,15 +236,15 @@
     <t xml:space="preserve">Hundepool et al, s. 220 </t>
   </si>
   <si>
+    <t>Verdiene for p og q fastsettes av statistikkmyndigheten og uttrykker hvilket nivå av informasjonsgevinst som aksepteres.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Regelen er et spesialtilfelle av (p, q)-regelen der q er satt til 100. </t>
   </si>
   <si>
     <t>Hundepool et al, s. 220; Heldal (Ordliste)</t>
   </si>
   <si>
-    <t>Regel som sier at en celle må undertrykkes hvis den nest største bidragsyteren til celletotalen kan estimere det største bidrag til celletotalen innenfor p% av den faktiske verdien.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Regel som sier at en celle må undertrykkes hvis informasjonsgevinsten publisering vil gi gjør det mulig å estimere en enhets bidrag til cellen i for stor grad. Informasjonsgevinsten ved publisering måles ved forholdet mellom feilmarginen etter (p) og før (q) publisering. </t>
   </si>
   <si>
@@ -266,19 +254,13 @@
     <t>(Random) rounding</t>
   </si>
   <si>
-    <t xml:space="preserve">Celleverdien erstattes ofte med et symbol for å vise at den har blitt undertrykket. Undertrykking kalles ofte for "prikking". </t>
-  </si>
-  <si>
     <t>En metode for å beskytte mot avsløring der verdiene i et datasett eller en tabell endres for å bevisst introdusere usikkerhet. De statistiske egenskapene til dataen bevares best mulig.</t>
   </si>
   <si>
-    <t>Noise addition/Perturbation based disclosure control methods</t>
-  </si>
-  <si>
     <t>Hundepool et al, s. 219; Heldal (Ordliste)</t>
   </si>
   <si>
-    <t xml:space="preserve">En regel som sier at en celle i en frekvenstabell ikke kan publiseres dersom antallet enheter i cellen er lavere enn en fastsatt terskel. </t>
+    <t>Pseudonymiserte personopplysninger er ikke anonyme.</t>
   </si>
   <si>
     <t xml:space="preserve">Avidentifisering av personopplysninger ved at direkte identifiserende parametere erstattes med pseudonymer, slik at de ikke kan knyttes til en bestemt person uten bruk av tilleggsopplysninger. </t>
@@ -287,16 +269,46 @@
     <t>https://www.ssb.no/teknologi-og-innovasjon/metoder-og-dokumentasjon/datatilstander-ssb</t>
   </si>
   <si>
-    <t>Variabel som alene eller i kombinasjon er strukturelt unik og dermed kan brukes til å identifisere statistiske enheter i et datasett.</t>
-  </si>
-  <si>
-    <t>Undertrykking er en metode for å hindre avsløring der enkelte celleverdier ikke publiseres. Primærundertrykking innebærer at celler med færre enheter enn en gitt terskel, eller der et lite antall enheter bidrar med en for stor andel av celletotalen, ikke publiseres. For å hindre at de undertrykte verdiene kan utledes, må ofte også andre celler undertrykkes. Dette kalles sekundærundertrykking.</t>
-  </si>
-  <si>
-    <t>Pseudonymiserte personopplysninger er ikke anonyme og er fortsatt personopplysninger.</t>
-  </si>
-  <si>
-    <t>Verdiene for p og q fastsettes av statistikkmyndigheten.</t>
+    <t>Inntrenger</t>
+  </si>
+  <si>
+    <t>Kilder</t>
+  </si>
+  <si>
+    <t>Avidentifisert data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Situasjon som oppstår dersom en person eller organisasjon ved hjelp av data lærer noe den ikke visste fra før om en statistisk enhet. </t>
+  </si>
+  <si>
+    <t>Regel som sier at en celle må undertrykkes hvis den nest største bidragsyteren til celletotalen kan estimere det største bidraget til celletotalen innenfor p% av den faktiske verdien.</t>
+  </si>
+  <si>
+    <t>Noise addition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regel som sier at en celle i en frekvenstabell ikke kan publiseres dersom antallet enheter i cellen er lavere enn en fastsatt terskel. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undertrykking av celler som inneholder færre enheter enn en gitt terskel, eller der et lite antall enheter bidrar med en for stor andel av celletotalen. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undertrykking av celler for å forhindre at celleverdier som har blitt primærundertrykket kan utledes. </t>
+  </si>
+  <si>
+    <t>Primary suppression</t>
+  </si>
+  <si>
+    <t>Secondary suppression</t>
+  </si>
+  <si>
+    <t>Sekundærundertrykking</t>
+  </si>
+  <si>
+    <t>Primærundertrykking</t>
+  </si>
+  <si>
+    <t>En metode for å hindre avsløring der enkelte tall ikke offentliggjøres, men erstattes med et symbol for å vise at den har blitt undertrykket. Undertrykking kalles ofte for "prikking".</t>
   </si>
 </sst>
 </file>
@@ -356,9 +368,7 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -414,7 +424,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -437,7 +447,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -747,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="28" customWidth="1"/>
@@ -758,14 +771,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -781,471 +794,489 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>76</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="D22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
     </row>
     <row r="27" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
     </row>
     <row r="28" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
     </row>
     <row r="29" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
     </row>
     <row r="31" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
     </row>
     <row r="32" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
     </row>
     <row r="33" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
     </row>
     <row r="34" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
     </row>
     <row r="35" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
     </row>
     <row r="36" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
     </row>
     <row r="37" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2"/>
@@ -1256,316 +1287,316 @@
       <c r="F37" s="2"/>
     </row>
     <row r="38" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
     </row>
     <row r="39" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
     </row>
     <row r="40" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
     </row>
     <row r="41" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
     </row>
     <row r="42" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
     </row>
     <row r="43" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
     </row>
     <row r="44" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
     </row>
     <row r="45" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
     </row>
     <row r="46" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
     </row>
     <row r="47" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
     </row>
     <row r="48" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
     </row>
     <row r="49" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
     </row>
     <row r="50" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
     </row>
     <row r="51" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
     </row>
     <row r="52" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
     </row>
     <row r="53" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
     </row>
     <row r="54" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
     </row>
     <row r="55" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
     </row>
     <row r="56" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
     </row>
     <row r="57" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
     </row>
     <row r="58" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
     </row>
     <row r="59" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
     </row>
     <row r="60" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
     </row>
     <row r="61" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
     </row>
     <row r="62" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
     </row>
     <row r="63" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
     </row>
     <row r="64" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
     </row>
     <row r="65" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
     </row>
     <row r="66" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
     </row>
     <row r="67" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
     </row>
     <row r="68" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
     </row>
     <row r="69" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
     </row>
     <row r="70" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
     </row>
     <row r="71" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
     </row>
     <row r="72" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
     </row>
     <row r="73" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
     </row>
     <row r="74" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
     </row>
     <row r="75" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
     </row>
     <row r="76" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
     </row>
     <row r="77" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
@@ -1576,84 +1607,84 @@
       <c r="F77" s="3"/>
     </row>
     <row r="78" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
     </row>
     <row r="79" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
     </row>
     <row r="80" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
     </row>
     <row r="81" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
     </row>
     <row r="82" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
     </row>
     <row r="83" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
     </row>
     <row r="84" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
     </row>
     <row r="85" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
     </row>
     <row r="86" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
     </row>
     <row r="87" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
     </row>
     <row r="88" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
@@ -1664,28 +1695,28 @@
       <c r="F88" s="3"/>
     </row>
     <row r="89" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
     </row>
     <row r="90" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
     </row>
     <row r="91" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
     </row>
     <row r="92" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2"/>
@@ -1696,92 +1727,92 @@
       <c r="F92" s="2"/>
     </row>
     <row r="93" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
     </row>
     <row r="94" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
     </row>
     <row r="95" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
     </row>
     <row r="96" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
     </row>
     <row r="97" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
     </row>
     <row r="98" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
     </row>
     <row r="99" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
     </row>
     <row r="100" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
     </row>
     <row r="101" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
     </row>
     <row r="102" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
     </row>
     <row r="103" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="2"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
     </row>
     <row r="104" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
@@ -1800,12 +1831,12 @@
       <c r="F105" s="3"/>
     </row>
     <row r="106" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="3"/>
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-      <c r="F106" s="3"/>
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
     </row>
     <row r="107" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2"/>
@@ -1816,44 +1847,44 @@
       <c r="F107" s="2"/>
     </row>
     <row r="108" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
     </row>
     <row r="109" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="3"/>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
     </row>
     <row r="110" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="2"/>
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
     </row>
     <row r="111" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="3"/>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
     </row>
     <row r="112" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
     </row>
     <row r="113" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3"/>
@@ -1872,28 +1903,28 @@
       <c r="F114" s="3"/>
     </row>
     <row r="115" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="3"/>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
     </row>
     <row r="116" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
     </row>
     <row r="117" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="3"/>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
     </row>
     <row r="118" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2"/>
@@ -1902,14 +1933,6 @@
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
-    </row>
-    <row r="119" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="2"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:F2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1920,5 +1943,6 @@
     <hyperlink ref="E20" r:id="rId1" xr:uid="{454E9478-C493-4D1F-969F-203728E70B25}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="0" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/ordbok_konfidensialitet.xlsx
+++ b/data/ordbok_konfidensialitet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ssbno-my.sharepoint.com/personal/ibi_ssb_no/Documents/Skrivebord/Ordbok Ingrid/Utkast ordbok/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="8_{19116777-D8DD-4556-9A16-9CDC6F0D346F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EF8CADD-821F-4779-B0C7-28DB987C048F}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="8_{19116777-D8DD-4556-9A16-9CDC6F0D346F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52D27DDF-57AD-462B-B0F5-22C3748E6BEC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,9 +167,6 @@
     <t>Data der direkte identifikatorer som navn, fødselsnummer eller andre entydige kjennetegn er fjernet, slik at identifisering av enkeltpersoner eller andre statistiske enheter er vanskeliggjort.</t>
   </si>
   <si>
-    <t>Data der det ikke er mulig, ved hjelp av de opplysningene som inngår i datasettet og alle rimelige tekniske hjelpemidler, å knytte opplysningene direkte eller indirekte til en enkeltperson eller en annen statistisk enhet.</t>
-  </si>
-  <si>
     <t>Opplysningene regnes fortsatt som lovregulerte personopplysninger. </t>
   </si>
   <si>
@@ -179,9 +176,6 @@
     <t>Hundepool et al, s. 212</t>
   </si>
   <si>
-    <t>En metode der celleverdier avrundes tilfeldig opp eller ned til et av de to nærmeste multiplene av et gitt basetall.</t>
-  </si>
-  <si>
     <t>Dette vil gi noen avvik fra de opprinnelige tallene, men metoden fungerer slik at avvikene er små og ikke betyr mye for tolkningen av resultatene.</t>
   </si>
   <si>
@@ -209,18 +203,6 @@
     <t>Hundepool et al, s. 215; Heldal (Ordliste)</t>
   </si>
   <si>
-    <t>Variabel som alene eller i kombinasjon er strukturelt unik(e) og dermed kan brukes til å identifisere statistiske enheter i et datasett.</t>
-  </si>
-  <si>
-    <t>Regel som sier at en celle må undertrykkes dersom de n største enhetene bidrar med mer enn k% av celletotalen. Verdiene for n og k fastsettes av statistikkmyndigheten.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regelen kalles ofte for (n, k)-regelen. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">En metode for å hindre avsløring der rader eller kolonner i tabeller slås sammen ved å lage større intervaller eller grupperinger, eller der flere variabelkategorier i mikrodata slås sammen til én kategori.  </t>
-  </si>
-  <si>
     <t>Hundepool et al, s. 216; Heldal (Ordliste)</t>
   </si>
   <si>
@@ -254,9 +236,6 @@
     <t>(Random) rounding</t>
   </si>
   <si>
-    <t>En metode for å beskytte mot avsløring der verdiene i et datasett eller en tabell endres for å bevisst introdusere usikkerhet. De statistiske egenskapene til dataen bevares best mulig.</t>
-  </si>
-  <si>
     <t>Hundepool et al, s. 219; Heldal (Ordliste)</t>
   </si>
   <si>
@@ -287,9 +266,6 @@
     <t>Noise addition</t>
   </si>
   <si>
-    <t xml:space="preserve">Regel som sier at en celle i en frekvenstabell ikke kan publiseres dersom antallet enheter i cellen er lavere enn en fastsatt terskel. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Undertrykking av celler som inneholder færre enheter enn en gitt terskel, eller der et lite antall enheter bidrar med en for stor andel av celletotalen. </t>
   </si>
   <si>
@@ -308,7 +284,31 @@
     <t>Primærundertrykking</t>
   </si>
   <si>
-    <t>En metode for å hindre avsløring der enkelte tall ikke offentliggjøres, men erstattes med et symbol for å vise at den har blitt undertrykket. Undertrykking kalles ofte for "prikking".</t>
+    <t xml:space="preserve">Regel som sier at en celle i en frekvenstabell ikke kan publiseres dersom antallet enheter i cellen er lavere enn en fastsatt terskel, og at en celle i en volumtabell ikke kan publiseres dersom antallet enheter som bidrar til celletotalen er under en fastsatt terskel. </t>
+  </si>
+  <si>
+    <t>En metode for å hindre avsløring der verdiene i et datasett eller en tabell endres for å bevisst introdusere usikkerhet. De statistiske egenskapene til dataen bevares best mulig.</t>
+  </si>
+  <si>
+    <t>En metode for å hindre avsløring der enkelte celleverdier ikke offentliggjøres, men erstattes med et symbol for å vise at de har blitt undertrykket. Undertrykking kalles ofte for "prikking".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En metode for å hindre avsløring der rader eller kolonner i tabeller slås sammen ved å lage større intervaller eller grupperinger, eller der flere variabelkategorier i mikrodata slås sammen.  </t>
+  </si>
+  <si>
+    <t>Regel som sier at en celle må undertrykkes dersom de n største enhetene bidrar med mer enn k% av celletotalen.</t>
+  </si>
+  <si>
+    <t>Regelen kalles ofte for (n, k)-regelen.  Verdiene for n og k fastsettes av statistikkmyndigheten.</t>
+  </si>
+  <si>
+    <t>Variabel som alene eller i kombinasjon er strukturelt unik og dermed kan brukes til å identifisere statistiske enheter i et datasett.</t>
+  </si>
+  <si>
+    <t>En metode der celleverdier avrundes tilfeldig opp eller ned til en av de nærmeste multiplene av et gitt basetall.</t>
+  </si>
+  <si>
+    <t>Data der det ikke er mulig, ved hjelp av de opplysningene som inngår i datasettet og alle rimelige tekniske hjelpemidler, å knytte opplysningene til en enkeltperson eller en annen statistisk enhet.</t>
   </si>
 </sst>
 </file>
@@ -794,7 +794,7 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
@@ -808,7 +808,7 @@
         <v>39</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>7</v>
@@ -817,7 +817,7 @@
         <v>41</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
@@ -832,13 +832,13 @@
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>8</v>
@@ -853,27 +853,27 @@
         <v>41</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
@@ -884,11 +884,11 @@
         <v>12</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F7" s="5"/>
     </row>
@@ -900,29 +900,29 @@
         <v>25</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F9" s="5"/>
     </row>
@@ -934,13 +934,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -952,11 +952,11 @@
         <v>34</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F11" s="5"/>
     </row>
@@ -968,16 +968,16 @@
         <v>16</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
@@ -988,13 +988,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F13" s="4"/>
     </row>
@@ -1006,13 +1006,13 @@
         <v>21</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>40</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F14" s="5"/>
     </row>
@@ -1024,13 +1024,13 @@
         <v>26</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F15" s="4"/>
     </row>
@@ -1042,16 +1042,16 @@
         <v>35</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
@@ -1062,16 +1062,16 @@
         <v>36</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
@@ -1079,16 +1079,16 @@
         <v>32</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F18" s="4"/>
     </row>
@@ -1100,13 +1100,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F19" s="4"/>
     </row>
@@ -1118,51 +1118,51 @@
         <v>37</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>40</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F22" s="4"/>
     </row>
